--- a/01_data/rainfall/rainfall_metadata.xlsx
+++ b/01_data/rainfall/rainfall_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/margaretswift/Documents/03 Science/00 Research - Active/Ecosphere Waterholes/eco-kaza-water-ele/01_data/rainfall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEB34D6-23C5-D94E-BC6A-6C316E708286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC4FCFD-E3EB-004F-A939-26E17A88ACF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="-7880" windowWidth="20020" windowHeight="21100" activeTab="2" xr2:uid="{36B2674D-5574-5749-ABD1-0B06D0B52360}"/>
+    <workbookView xWindow="29400" yWindow="-7880" windowWidth="20020" windowHeight="21100" activeTab="1" xr2:uid="{36B2674D-5574-5749-ABD1-0B06D0B52360}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="38">
   <si>
     <t>Data location</t>
   </si>
@@ -132,34 +132,10 @@
     <t>GEE multipoint coordinate data</t>
   </si>
   <si>
-    <t>00000000000000000000</t>
-  </si>
-  <si>
-    <t>460.9407513225366</t>
-  </si>
-  <si>
-    <t>592.5943139492646</t>
-  </si>
-  <si>
-    <t>705.6905494114842</t>
-  </si>
-  <si>
-    <t>763.7042525250564</t>
-  </si>
-  <si>
-    <t>644.4067148214054</t>
-  </si>
-  <si>
-    <t>553.1722651963681</t>
-  </si>
-  <si>
-    <t>543.7386959422189</t>
-  </si>
-  <si>
-    <t>/01_data/rainfall/raw/Hydroshed_Mar</t>
-  </si>
-  <si>
     <t>Mean Annual Rainfall (MAR) from Hydrosheds</t>
+  </si>
+  <si>
+    <t>/01_data/rainfall/raw/Hydroshed_MAR</t>
   </si>
 </sst>
 </file>
@@ -1078,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD10E182-381E-134C-8934-448426DD1D39}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -1259,85 +1235,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2019</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>2020</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>2021</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>2022</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>2023</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>2024</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>2025</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28">
-        <v>1051431680</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B26" s="6"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1360,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D1" s="3"/>
     </row>
@@ -1369,7 +1289,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3"/>
     </row>
